--- a/src/mirror/sensor_KP/mirror3_data/sensor_data.xlsx
+++ b/src/mirror/sensor_KP/mirror3_data/sensor_data.xlsx
@@ -423,6 +423,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -725,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -951,7 +1101,7 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260729_153223</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -966,22 +1116,22 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>motor1_data_20260729_153223_拟合图</t>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>y=4009x+1</t>
+          <t>y=4008x+1</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4009</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260729_153223</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -996,16 +1146,16 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>motor1_data_20260729_153223_拟合图</t>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>y=4009x+1</t>
+          <t>y=4008x+1</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4009</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -1091,7 +1241,7 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260729_154924</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1106,22 +1256,22 @@
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>motor1_data_20260729_154924_拟合图</t>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>y=4018x+1</t>
+          <t>y=4009x+1</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4018</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260729_154924</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1152,16 +1302,16 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>motor1_data_20260729_154924_拟合图</t>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>y=4018x+1</t>
+          <t>y=4009x+1</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4018</v>
+        <v>4009</v>
       </c>
       <c r="K11">
         <f>AVERAGE(J11:J13)</f>
@@ -1171,7 +1321,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260729_154924</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1186,67 +1336,297 @@
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>motor1_data_20260729_154924_拟合图</t>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>y=4018x+1</t>
+          <t>y=4009x+1</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4018</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
+          <t>20260729_153223</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_153223_拟合图</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>y=4009x+1</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>20260729_154924</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[-150N, 150N]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[0, -20W, -5K]</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>192.168.0.100:1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>motor1_data_20260729_154924_拟合图</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>y=4018x+1</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>4018</v>
       </c>
+      <c r="K14">
+        <f>AVERAGE(J14:J16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260729_154924</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260729_154924</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260729_154924</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>192.168.0.100:1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4018</v>
+      </c>
+      <c r="K17">
+        <f>AVERAGE(J17:J19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260729_154924</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260729_154924</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4018</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="30">
     <mergeCell ref="D5:D7"/>
+    <mergeCell ref="K17:K19"/>
     <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C17:C19"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="C11:C13"/>
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="D8:D10"/>
+    <mergeCell ref="K14:K16"/>
     <mergeCell ref="B5:B7"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E17:E19"/>
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="K11:K13"/>
+    <mergeCell ref="C14:C16"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="K5:K7"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="D17:D19"/>
     <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B17:B19"/>
     <mergeCell ref="D11:D13"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="K8:K10"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="E2:E4"/>
